--- a/dati/CONSEGNE/CONSEGNE_30-03-2026_31-03-2026/punti_consegna.xlsx
+++ b/dati/CONSEGNE/CONSEGNE_30-03-2026_31-03-2026/punti_consegna.xlsx
@@ -476,12 +476,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>p1937</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>p10949_p1937</t>
+          <t>p10949_p00000</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -522,12 +522,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>p1831</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p11205_p1831</t>
+          <t>p11205_p00000</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -660,12 +660,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>p1906</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>p2044_p1906</t>
+          <t>p2044_p00000</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>p1745</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>p2063_p1745</t>
+          <t>p2063_p00000</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -890,12 +890,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>p1764</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>p2140_p1764</t>
+          <t>p2140_p00000</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -982,12 +982,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p1840</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>p2155_p1840</t>
+          <t>p2155_p00000</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>p1914</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>p2169_p1914</t>
+          <t>p2169_p00000</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>p1700</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>p2233_p1700</t>
+          <t>p2233_p00000</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>p1767</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>p2320_p1767</t>
+          <t>p2320_p00000</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>p1768</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>p2321_p1768</t>
+          <t>p2321_p00000</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>p2641</t>
+          <t>p00000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>p6917_p2641</t>
+          <t>p6917_p00000</t>
         </is>
       </c>
       <c r="D19" t="n">
